--- a/04_CFD/00_XFLR5/Nalci&Kayran/Mach 0_6 0 msnm.xlsx
+++ b/04_CFD/00_XFLR5/Nalci&Kayran/Mach 0_6 0 msnm.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udeconce-my.sharepoint.com/personal/joarriagada2021_udec_cl/Documents/Escritorio/Memoria/04_CFD/00_XFLR5/Nalci&amp;Kayran/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{C5454BC3-CCFB-400C-9117-5DF7B11ACEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E01EE9A-B53E-4BD3-814A-EFAB973CAC53}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{C5454BC3-CCFB-400C-9117-5DF7B11ACEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFABAF6C-97CA-4D57-8E9B-A030B0DAE01B}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{65ACA0F2-BEA7-4788-8767-0101B11265C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{65ACA0F2-BEA7-4788-8767-0101B11265C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Mach 0_6 0 msnm" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1087,8 +1100,8 @@
         <v>25539.804499999998</v>
       </c>
       <c r="O8">
-        <f>I8*N8*0.18*0.121333</f>
-        <v>-43.595020919823945</v>
+        <f>I8*N8*0.018*0.121333</f>
+        <v>-4.3595020919823932</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1136,8 +1149,8 @@
         <v>25539.804499999998</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O72" si="1">I9*N9*0.18*0.121333</f>
-        <v>-42.934042379322236</v>
+        <f t="shared" ref="O9:O72" si="1">I9*N9*0.018*0.121333</f>
+        <v>-4.293404237932223</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1186,7 +1199,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="1"/>
-        <v>-42.269159324235297</v>
+        <v>-4.2269159324235286</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1235,7 +1248,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="1"/>
-        <v>-41.601487330158889</v>
+        <v>-4.1601487330158893</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1284,7 +1297,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="1"/>
-        <v>-40.93046860929514</v>
+        <v>-4.0930468609295145</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1333,7 +1346,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="1"/>
-        <v>-40.25666094944193</v>
+        <v>-4.0256660949441931</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1382,7 +1395,7 @@
       </c>
       <c r="O14">
         <f t="shared" si="1"/>
-        <v>-39.57950656280137</v>
+        <v>-3.9579506562801368</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1431,7 +1444,7 @@
       </c>
       <c r="O15">
         <f t="shared" si="1"/>
-        <v>-38.899563237171343</v>
+        <v>-3.8899563237171351</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1480,7 +1493,7 @@
       </c>
       <c r="O16">
         <f t="shared" si="1"/>
-        <v>-38.216830972551875</v>
+        <v>-3.8216830972551881</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1529,7 +1542,7 @@
       </c>
       <c r="O17">
         <f t="shared" si="1"/>
-        <v>-37.530751981145052</v>
+        <v>-3.7530751981145047</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1578,7 +1591,7 @@
       </c>
       <c r="O18">
         <f t="shared" si="1"/>
-        <v>-36.84188405074876</v>
+        <v>-3.6841884050748761</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1627,7 +1640,7 @@
       </c>
       <c r="O19">
         <f t="shared" si="1"/>
-        <v>-36.150784969160902</v>
+        <v>-3.6150784969160901</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1676,7 +1689,7 @@
       </c>
       <c r="O20">
         <f t="shared" si="1"/>
-        <v>-35.456339160785703</v>
+        <v>-3.5456339160785699</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1725,7 +1738,7 @@
       </c>
       <c r="O21">
         <f t="shared" si="1"/>
-        <v>-34.759662201218937</v>
+        <v>-3.4759662201218933</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1774,7 +1787,7 @@
       </c>
       <c r="O22">
         <f t="shared" si="1"/>
-        <v>-34.06019630266271</v>
+        <v>-3.4060196302662704</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1823,7 +1836,7 @@
       </c>
       <c r="O23">
         <f t="shared" si="1"/>
-        <v>-33.357941465117023</v>
+        <v>-3.3357941465117023</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1872,7 +1885,7 @@
       </c>
       <c r="O24">
         <f t="shared" si="1"/>
-        <v>-32.653455476379762</v>
+        <v>-3.2653455476379762</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1921,7 +1934,7 @@
       </c>
       <c r="O25">
         <f t="shared" si="1"/>
-        <v>-31.946180548653047</v>
+        <v>-3.194618054865304</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1970,7 +1983,7 @@
       </c>
       <c r="O26">
         <f t="shared" si="1"/>
-        <v>-31.236674469734773</v>
+        <v>-3.1236674469734771</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -2019,7 +2032,7 @@
       </c>
       <c r="O27">
         <f t="shared" si="1"/>
-        <v>-30.524937239624922</v>
+        <v>-3.0524937239624923</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -2068,7 +2081,7 @@
       </c>
       <c r="O28">
         <f t="shared" si="1"/>
-        <v>-29.810968858323502</v>
+        <v>-2.9810968858323506</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -2117,7 +2130,7 @@
       </c>
       <c r="O29">
         <f t="shared" si="1"/>
-        <v>-29.094769325830523</v>
+        <v>-2.9094769325830523</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -2166,7 +2179,7 @@
       </c>
       <c r="O30">
         <f t="shared" si="1"/>
-        <v>-28.375780854348083</v>
+        <v>-2.8375780854348083</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -2215,7 +2228,7 @@
       </c>
       <c r="O31">
         <f t="shared" si="1"/>
-        <v>-27.655119019471968</v>
+        <v>-2.765511901947197</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -2264,7 +2277,7 @@
       </c>
       <c r="O32">
         <f t="shared" si="1"/>
-        <v>-26.932783821202182</v>
+        <v>-2.693278382120218</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2313,7 +2326,7 @@
       </c>
       <c r="O33">
         <f t="shared" si="1"/>
-        <v>-26.207659683942929</v>
+        <v>-2.6207659683942928</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -2362,7 +2375,7 @@
       </c>
       <c r="O34">
         <f t="shared" si="1"/>
-        <v>-25.480862183290007</v>
+        <v>-2.5480862183290007</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -2411,7 +2424,7 @@
       </c>
       <c r="O35">
         <f t="shared" si="1"/>
-        <v>-24.752391319243404</v>
+        <v>-2.4752391319243401</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -2460,7 +2473,7 @@
       </c>
       <c r="O36">
         <f t="shared" si="1"/>
-        <v>-24.021689304005239</v>
+        <v>-2.4021689304005238</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -2509,7 +2522,7 @@
       </c>
       <c r="O37">
         <f t="shared" si="1"/>
-        <v>-23.289313925373399</v>
+        <v>-2.3289313925373394</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -2558,7 +2571,7 @@
       </c>
       <c r="O38">
         <f t="shared" si="1"/>
-        <v>-22.555265183347881</v>
+        <v>-2.2555265183347881</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -2607,7 +2620,7 @@
       </c>
       <c r="O39">
         <f t="shared" si="1"/>
-        <v>-21.819543077928692</v>
+        <v>-2.1819543077928691</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -2656,7 +2669,7 @@
       </c>
       <c r="O40">
         <f t="shared" si="1"/>
-        <v>-21.082147609115825</v>
+        <v>-2.1082147609115829</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -2705,7 +2718,7 @@
       </c>
       <c r="O41">
         <f t="shared" si="1"/>
-        <v>-20.343078776909287</v>
+        <v>-2.0343078776909285</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2754,7 +2767,7 @@
       </c>
       <c r="O42">
         <f t="shared" si="1"/>
-        <v>-19.602336581309064</v>
+        <v>-1.9602336581309063</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2803,7 +2816,7 @@
       </c>
       <c r="O43">
         <f t="shared" si="1"/>
-        <v>-18.860478810113065</v>
+        <v>-1.8860478810113066</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2852,7 +2865,7 @@
       </c>
       <c r="O44">
         <f t="shared" si="1"/>
-        <v>-18.116947675523388</v>
+        <v>-1.8116947675523387</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -2901,7 +2914,7 @@
       </c>
       <c r="O45">
         <f t="shared" si="1"/>
-        <v>-17.372300965337928</v>
+        <v>-1.7372300965337928</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -2950,7 +2963,7 @@
       </c>
       <c r="O46">
         <f t="shared" si="1"/>
-        <v>-16.626538679556688</v>
+        <v>-1.6626538679556686</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -2999,7 +3012,7 @@
       </c>
       <c r="O47">
         <f t="shared" si="1"/>
-        <v>-15.879103030381767</v>
+        <v>-1.5879103030381767</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -3048,7 +3061,7 @@
       </c>
       <c r="O48">
         <f t="shared" si="1"/>
-        <v>-15.130551805611068</v>
+        <v>-1.5130551805611068</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -3097,7 +3110,7 @@
       </c>
       <c r="O49">
         <f t="shared" si="1"/>
-        <v>-14.380885005244581</v>
+        <v>-1.4380885005244581</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -3146,7 +3159,7 @@
       </c>
       <c r="O50">
         <f t="shared" si="1"/>
-        <v>-13.630102629282312</v>
+        <v>-1.3630102629282312</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -3195,7 +3208,7 @@
       </c>
       <c r="O51">
         <f t="shared" si="1"/>
-        <v>-12.878762465522151</v>
+        <v>-1.2878762465522151</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -3244,7 +3257,7 @@
       </c>
       <c r="O52">
         <f t="shared" si="1"/>
-        <v>-12.125748938368318</v>
+        <v>-1.2125748938368319</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -3293,7 +3306,7 @@
       </c>
       <c r="O53">
         <f t="shared" si="1"/>
-        <v>-11.372177623416592</v>
+        <v>-1.1372177623416591</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -3342,7 +3355,7 @@
       </c>
       <c r="O54">
         <f t="shared" si="1"/>
-        <v>-10.618048520666971</v>
+        <v>-1.0618048520666972</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -3391,7 +3404,7 @@
       </c>
       <c r="O55">
         <f t="shared" si="1"/>
-        <v>-9.8628038423215703</v>
+        <v>-0.98628038423215691</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -3440,7 +3453,7 @@
       </c>
       <c r="O56">
         <f t="shared" si="1"/>
-        <v>-9.1070013761782747</v>
+        <v>-0.91070013761782753</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -3489,7 +3502,7 @@
       </c>
       <c r="O57">
         <f t="shared" si="1"/>
-        <v>-8.3500833344391978</v>
+        <v>-0.83500833344391978</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -3538,7 +3551,7 @@
       </c>
       <c r="O58">
         <f t="shared" si="1"/>
-        <v>-7.5931652927001201</v>
+        <v>-0.75931652927001192</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -3587,7 +3600,7 @@
       </c>
       <c r="O59">
         <f t="shared" si="1"/>
-        <v>-6.8351316753652585</v>
+        <v>-0.6835131675365258</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -3636,7 +3649,7 @@
       </c>
       <c r="O60">
         <f t="shared" si="1"/>
-        <v>-6.0770980580303977</v>
+        <v>-0.60770980580303979</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -3685,7 +3698,7 @@
       </c>
       <c r="O61">
         <f t="shared" si="1"/>
-        <v>-5.3185066528976446</v>
+        <v>-0.53185066528976455</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -3734,7 +3747,7 @@
       </c>
       <c r="O62">
         <f t="shared" si="1"/>
-        <v>-4.5593574599670008</v>
+        <v>-0.45593574599670006</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -3783,7 +3796,7 @@
       </c>
       <c r="O63">
         <f t="shared" si="1"/>
-        <v>-3.7996504792384642</v>
+        <v>-0.37996504792384639</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -3832,7 +3845,7 @@
       </c>
       <c r="O64">
         <f t="shared" si="1"/>
-        <v>-3.0399434985099281</v>
+        <v>-0.30399434985099283</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -3881,7 +3894,7 @@
       </c>
       <c r="O65">
         <f t="shared" si="1"/>
-        <v>-2.2802365177813919</v>
+        <v>-0.22802365177813919</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -3930,7 +3943,7 @@
       </c>
       <c r="O66">
         <f t="shared" si="1"/>
-        <v>-1.519971749254964</v>
+        <v>-0.15199717492549641</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
@@ -3979,7 +3992,7 @@
       </c>
       <c r="O67">
         <f t="shared" si="1"/>
-        <v>-0.76026476852642788</v>
+        <v>-7.6026476852642785E-2</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -4077,7 +4090,7 @@
       </c>
       <c r="O69">
         <f t="shared" si="1"/>
-        <v>0.76026476852642788</v>
+        <v>7.6026476852642785E-2</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -4126,7 +4139,7 @@
       </c>
       <c r="O70">
         <f t="shared" si="1"/>
-        <v>1.519971749254964</v>
+        <v>0.15199717492549641</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
@@ -4175,7 +4188,7 @@
       </c>
       <c r="O71">
         <f t="shared" si="1"/>
-        <v>2.2802365177813919</v>
+        <v>0.22802365177813919</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
@@ -4224,7 +4237,7 @@
       </c>
       <c r="O72">
         <f t="shared" si="1"/>
-        <v>3.0399434985099281</v>
+        <v>0.30399434985099283</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
@@ -4272,8 +4285,8 @@
         <v>25539.804499999998</v>
       </c>
       <c r="O73">
-        <f t="shared" ref="O73:O128" si="3">I73*N73*0.18*0.121333</f>
-        <v>3.7990926914405723</v>
+        <f t="shared" ref="O73:O128" si="3">I73*N73*0.018*0.121333</f>
+        <v>0.37990926914405726</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
@@ -4322,7 +4335,7 @@
       </c>
       <c r="O74">
         <f t="shared" si="3"/>
-        <v>4.5582418843712178</v>
+        <v>0.45582418843712175</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
@@ -4371,7 +4384,7 @@
       </c>
       <c r="O75">
         <f t="shared" si="3"/>
-        <v>5.3168332895039701</v>
+        <v>0.53168332895039705</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
@@ -4420,7 +4433,7 @@
       </c>
       <c r="O76">
         <f t="shared" si="3"/>
-        <v>6.0754246946367232</v>
+        <v>0.60754246946367219</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
@@ -4469,7 +4482,7 @@
       </c>
       <c r="O77">
         <f t="shared" si="3"/>
-        <v>6.833458311971583</v>
+        <v>0.68334583119715819</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
@@ -4518,7 +4531,7 @@
       </c>
       <c r="O78">
         <f t="shared" si="3"/>
-        <v>7.5903763537106608</v>
+        <v>0.75903763537106606</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
@@ -4567,7 +4580,7 @@
       </c>
       <c r="O79">
         <f t="shared" si="3"/>
-        <v>8.3472943954497367</v>
+        <v>0.83472943954497369</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
@@ -4616,7 +4629,7 @@
       </c>
       <c r="O80">
         <f t="shared" si="3"/>
-        <v>9.1030968615930341</v>
+        <v>0.9103096861593033</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
@@ -4665,7 +4678,7 @@
       </c>
       <c r="O81">
         <f t="shared" si="3"/>
-        <v>9.8583415399384347</v>
+        <v>0.98583415399384344</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
@@ -4714,7 +4727,7 @@
       </c>
       <c r="O82">
         <f t="shared" si="3"/>
-        <v>10.613028430485944</v>
+        <v>1.0613028430485942</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
@@ -4763,7 +4776,7 @@
       </c>
       <c r="O83">
         <f t="shared" si="3"/>
-        <v>11.366599745437673</v>
+        <v>1.1366599745437673</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -4812,7 +4825,7 @@
       </c>
       <c r="O84">
         <f t="shared" si="3"/>
-        <v>12.11961327259151</v>
+        <v>1.211961327259151</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
@@ -4861,7 +4874,7 @@
       </c>
       <c r="O85">
         <f t="shared" si="3"/>
-        <v>12.871511224149559</v>
+        <v>1.2871511224149559</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
@@ -4910,7 +4923,7 @@
       </c>
       <c r="O86">
         <f t="shared" si="3"/>
-        <v>13.62229360011183</v>
+        <v>1.3622293600111828</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
@@ -4959,7 +4972,7 @@
       </c>
       <c r="O87">
         <f t="shared" si="3"/>
-        <v>14.371960400478313</v>
+        <v>1.4371960400478314</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
@@ -5008,7 +5021,7 @@
       </c>
       <c r="O88">
         <f t="shared" si="3"/>
-        <v>15.121069413046907</v>
+        <v>1.5121069413046906</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
@@ -5057,7 +5070,7 @@
       </c>
       <c r="O89">
         <f t="shared" si="3"/>
-        <v>15.868505062221827</v>
+        <v>1.5868505062221825</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
@@ -5106,7 +5119,7 @@
       </c>
       <c r="O90">
         <f t="shared" si="3"/>
-        <v>16.61482513580096</v>
+        <v>1.6614825135800959</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
@@ -5155,7 +5168,7 @@
       </c>
       <c r="O91">
         <f t="shared" si="3"/>
-        <v>17.359471845986416</v>
+        <v>1.7359471845986418</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
@@ -5204,7 +5217,7 @@
       </c>
       <c r="O92">
         <f t="shared" si="3"/>
-        <v>18.103002980576093</v>
+        <v>1.8103002980576091</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
@@ -5253,7 +5266,7 @@
       </c>
       <c r="O93">
         <f t="shared" si="3"/>
-        <v>18.845418539569987</v>
+        <v>1.8845418539569987</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
@@ -5302,7 +5315,7 @@
       </c>
       <c r="O94">
         <f t="shared" si="3"/>
-        <v>19.586160735170203</v>
+        <v>1.9586160735170206</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
@@ -5351,7 +5364,7 @@
       </c>
       <c r="O95">
         <f t="shared" si="3"/>
-        <v>20.32578735517464</v>
+        <v>2.0325787355174638</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
@@ -5400,7 +5413,7 @@
       </c>
       <c r="O96">
         <f t="shared" si="3"/>
-        <v>21.0631828239875</v>
+        <v>2.1063182823987501</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
@@ -5449,7 +5462,7 @@
       </c>
       <c r="O97">
         <f t="shared" si="3"/>
-        <v>21.799462717204587</v>
+        <v>2.1799462717204587</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
@@ -5498,7 +5511,7 @@
       </c>
       <c r="O98">
         <f t="shared" si="3"/>
-        <v>22.533511459230109</v>
+        <v>2.2533511459230109</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
@@ -5547,7 +5560,7 @@
       </c>
       <c r="O99">
         <f t="shared" si="3"/>
-        <v>23.26644462565984</v>
+        <v>2.3266444625659837</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
@@ -5596,7 +5609,7 @@
       </c>
       <c r="O100">
         <f t="shared" si="3"/>
-        <v>23.997146640898006</v>
+        <v>2.3997146640898004</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
@@ -5645,7 +5658,7 @@
       </c>
       <c r="O101">
         <f t="shared" si="3"/>
-        <v>24.726175292742496</v>
+        <v>2.4726175292742498</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
@@ -5694,7 +5707,7 @@
       </c>
       <c r="O102">
         <f t="shared" si="3"/>
-        <v>25.452972793395418</v>
+        <v>2.5452972793395419</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
@@ -5743,7 +5756,7 @@
       </c>
       <c r="O103">
         <f t="shared" si="3"/>
-        <v>26.178096930654672</v>
+        <v>2.6178096930654666</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
@@ -5792,7 +5805,7 @@
       </c>
       <c r="O104">
         <f t="shared" si="3"/>
-        <v>26.901547704520244</v>
+        <v>2.6901547704520241</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
@@ -5841,7 +5854,7 @@
       </c>
       <c r="O105">
         <f t="shared" si="3"/>
-        <v>27.62276732719425</v>
+        <v>2.7622767327194246</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -5890,7 +5903,7 @@
       </c>
       <c r="O106">
         <f t="shared" si="3"/>
-        <v>28.341198010878795</v>
+        <v>2.8341198010878794</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
@@ -5939,7 +5952,7 @@
       </c>
       <c r="O107">
         <f t="shared" si="3"/>
-        <v>29.057955331169673</v>
+        <v>2.9057955331169669</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
@@ -5988,7 +6001,7 @@
       </c>
       <c r="O108">
         <f t="shared" si="3"/>
-        <v>29.772481500268974</v>
+        <v>2.9772481500268975</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
@@ -6037,7 +6050,7 @@
       </c>
       <c r="O109">
         <f t="shared" si="3"/>
-        <v>30.484776518176716</v>
+        <v>3.0484776518176715</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
@@ -6086,7 +6099,7 @@
       </c>
       <c r="O110">
         <f t="shared" si="3"/>
-        <v>31.194840384892885</v>
+        <v>3.1194840384892886</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
@@ -6135,7 +6148,7 @@
       </c>
       <c r="O111">
         <f t="shared" si="3"/>
-        <v>31.902115312619603</v>
+        <v>3.1902115312619603</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
@@ -6184,7 +6197,7 @@
       </c>
       <c r="O112">
         <f t="shared" si="3"/>
-        <v>32.607159089154749</v>
+        <v>3.2607159089154747</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
@@ -6233,7 +6246,7 @@
       </c>
       <c r="O113">
         <f t="shared" si="3"/>
-        <v>33.309413926700437</v>
+        <v>3.3309413926700433</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
@@ -6282,7 +6295,7 @@
       </c>
       <c r="O114">
         <f t="shared" si="3"/>
-        <v>34.009437613054558</v>
+        <v>3.4009437613054554</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
@@ -6331,7 +6344,7 @@
       </c>
       <c r="O115">
         <f t="shared" si="3"/>
-        <v>34.706672360419219</v>
+        <v>3.4706672360419217</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
@@ -6380,7 +6393,7 @@
       </c>
       <c r="O116">
         <f t="shared" si="3"/>
-        <v>35.401675956592314</v>
+        <v>3.5401675956592311</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
@@ -6429,7 +6442,7 @@
       </c>
       <c r="O117">
         <f t="shared" si="3"/>
-        <v>36.093332825978059</v>
+        <v>3.6093332825978059</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
@@ -6478,7 +6491,7 @@
       </c>
       <c r="O118">
         <f t="shared" si="3"/>
-        <v>36.782758544172239</v>
+        <v>3.6782758544172234</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
@@ -6527,7 +6540,7 @@
       </c>
       <c r="O119">
         <f t="shared" si="3"/>
-        <v>37.46883753557907</v>
+        <v>3.7468837535579063</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
@@ -6576,7 +6589,7 @@
       </c>
       <c r="O120">
         <f t="shared" si="3"/>
-        <v>38.152127587996439</v>
+        <v>3.8152127587996438</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
@@ -6625,7 +6638,7 @@
       </c>
       <c r="O121">
         <f t="shared" si="3"/>
-        <v>38.832628701424348</v>
+        <v>3.8832628701424352</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
@@ -6674,7 +6687,7 @@
       </c>
       <c r="O122">
         <f t="shared" si="3"/>
-        <v>39.510340875862795</v>
+        <v>3.9510340875862791</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
@@ -6723,7 +6736,7 @@
       </c>
       <c r="O123">
         <f t="shared" si="3"/>
-        <v>40.1847063235139</v>
+        <v>4.0184706323513897</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
@@ -6772,7 +6785,7 @@
       </c>
       <c r="O124">
         <f t="shared" si="3"/>
-        <v>40.856282832175545</v>
+        <v>4.0856282832175541</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
@@ -6821,7 +6834,7 @@
       </c>
       <c r="O125">
         <f t="shared" si="3"/>
-        <v>41.524512614049833</v>
+        <v>4.1524512614049831</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
@@ -6870,7 +6883,7 @@
       </c>
       <c r="O126">
         <f t="shared" si="3"/>
-        <v>42.189395669136772</v>
+        <v>4.2189395669136776</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
@@ -6919,7 +6932,7 @@
       </c>
       <c r="O127">
         <f t="shared" si="3"/>
-        <v>42.851489785234264</v>
+        <v>4.2851489785234262</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
@@ -6968,7 +6981,7 @@
       </c>
       <c r="O128">
         <f t="shared" si="3"/>
-        <v>43.510237174544393</v>
+        <v>4.3510237174544386</v>
       </c>
     </row>
   </sheetData>
